--- a/settings.xlsx
+++ b/settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manager|Director|Payroll|Super Admin|Member</t>
+          <t>Manager|Director|Payroll|Super Admin|Team Member|Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>departments</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>National Grid|Isolator|Project|Accounts|Payroll Department|ACoole Electrical Ltd|Store</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Grid|Isolator|Project|Accounts|Payroll Department|ACoole Electrical Ltd|Store</t>
+          <t>National Grid|Isolator|Project|Accounts|Payroll Department|ACoole Electrical Ltd|Store|System Administrator</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Food Allowance|Others|Parking|Parking Fine|GYM Membership|Item Not Returned|Item Missing|Lost ID Card</t>
+          <t>Food Allowance|Others|Parking|Parking Fine|GYM Membership|Item Not Returned|Item Missing|Lost ID Card|Vehicle hire / Accommodation|Work boots|Fuel Expense|N2 card not returned|Specialised face mask|Hotel Expense|Lost equipment|Postage</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Food Allowance|Others|Parking|Parking Fine|GYM Membership|Item Not Returned|Item Missing|Lost ID Card|Vehicle hire / Accommodation|Work boots|Fuel Expense|N2 card not returned|Specialised face mask|Hotel Expense|Lost equipment|Postage</t>
+          <t>Food Allowance|Others|Parking|Parking Fine|GYM Membership|Unreturned Items|Item Missing|Work Boots|Fuel Expense|N2 card not returned|Specialised Face Mask|Hotel Expense|Lost Equipment|Postage|Key Battery|Advance Payment|Holiday Deduction</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manager|Director|Payroll|Super Admin|Team Member|Staff</t>
+          <t>Manager|Staff|Director|Payroll|Super Admin</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Grid|Isolator|Project|Accounts|Payroll Department|ACoole Electrical Ltd|Store|System Administrator</t>
+          <t>National Grid|Isolator|Projects|Accounts|Payroll Department|ACoole Electrical Ltd|System Administrator</t>
         </is>
       </c>
     </row>
